--- a/src/attributions/attributions_ig_traj_199.xlsx
+++ b/src/attributions/attributions_ig_traj_199.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG16"/>
+  <dimension ref="A1:GG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,19 +1571,19 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1685978277193575</v>
+        <v>0.4332680881740301</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0151198959754832</v>
+        <v>0.1091704889771342</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.161394370747136</v>
+        <v>-0.3977131828659938</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04755572348394541</v>
+        <v>0.1753590444344705</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.002807042665256548</v>
+        <v>-0.01425664320074542</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.02151707548685943</v>
+        <v>-0.04914568091986354</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
@@ -1625,46 +1625,46 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.002936139945189354</v>
+        <v>-0.1524665539012007</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.05557717244222276</v>
+        <v>-0.07431664906523569</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.005377667146446236</v>
+        <v>-0.1589906545431309</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05009159603742939</v>
+        <v>0.1016373071981574</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.04472782322440014</v>
+        <v>0.08848704575051348</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.006874389909797956</v>
+        <v>0.2188582469005623</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1679,76 +1679,76 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0204575978287466</v>
+        <v>0.1438091568678066</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.01214684190474318</v>
+        <v>-0.0328147400508173</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.05199961574270204</v>
+        <v>-0.2620668715892354</v>
       </c>
       <c r="AQ3" t="n">
         <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1811331160631621</v>
+        <v>0.4109286406079689</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.02983869464580163</v>
+        <v>-0.2382355804401239</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.1479472865526363</v>
+        <v>-0.4133893694386126</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.05788837861161806</v>
+        <v>0.1976353265722349</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.02304460196370412</v>
+        <v>0.09974731413268663</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.07388081647276558</v>
+        <v>-0.1804601576728224</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
@@ -1760,76 +1760,76 @@
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.02600165305687407</v>
+        <v>-0.001486149434038603</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.01133386064358824</v>
+        <v>0.1046662812032872</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.009149324988455087</v>
+        <v>0.183552648730084</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.05662743404773649</v>
+        <v>0.1794694898655896</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.03903512116657529</v>
+        <v>-0.09115813848621165</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.05424613326781513</v>
+        <v>-0.3316396204286618</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="n">
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.059732943763059</v>
+        <v>-0.2880543116310033</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.008325567071979149</v>
+        <v>-0.07311236354434807</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.06469911915438459</v>
+        <v>0.2131716123819617</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
@@ -1841,19 +1841,19 @@
         <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.01254194879425214</v>
+        <v>-0.3162961287151864</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.03751276848557811</v>
+        <v>0.1345610677566753</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01085990714000432</v>
+        <v>0.2422088516862793</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
@@ -1868,22 +1868,22 @@
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.04303544335468487</v>
+        <v>-0.2749716017632381</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0001302330125048754</v>
+        <v>-0.04562115997694555</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.07413813489325953</v>
+        <v>0.1875111139141362</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,52 +1892,52 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.07509270508392367</v>
+        <v>-0.1963060644455474</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
         <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.02135936451085691</v>
+        <v>-0.05341258633158077</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.001484761372163357</v>
+        <v>0.180049675593751</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.02825658735269271</v>
+        <v>-0.09342118973194168</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.05283488128186219</v>
+        <v>0.006027026613112886</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.01334066465198895</v>
+        <v>0.05785190011975216</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,22 +1946,22 @@
         <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.02065384349129177</v>
+        <v>0.1721066216826773</v>
       </c>
       <c r="DY3" t="n">
         <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0140844133204887</v>
+        <v>-0.06620152288448267</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.003205524083498438</v>
+        <v>0.1857205668699174</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
@@ -1973,25 +1973,25 @@
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0789736873880712</v>
+        <v>-0.1651026301209789</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.01186008434434099</v>
+        <v>-0.08272744553007591</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.07048538812824297</v>
+        <v>0.1790038937013823</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
@@ -2000,10 +2000,10 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.04986569033668355</v>
+        <v>-0.2035570394427266</v>
       </c>
       <c r="EQ3" t="n">
         <v>-0</v>
@@ -2012,16 +2012,16 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.03165760633777971</v>
+        <v>-0.233826531067799</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.04578108528886896</v>
+        <v>0.2056519112396599</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>-0</v>
@@ -2030,46 +2030,46 @@
         <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.04779688434047946</v>
+        <v>-0.2596220116454998</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01274640823956842</v>
+        <v>-0.1231874467754619</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.06192234663859664</v>
+        <v>0.1958485008840742</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.02907390299935221</v>
+        <v>-0.1151226995810746</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.04817857275785145</v>
+        <v>-0.063783231639164</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.06303047881796549</v>
+        <v>0.3559899713472209</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2081,58 +2081,58 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.1113650412406252</v>
+        <v>0.06243325443620584</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.0009074411102568673</v>
+        <v>0.02746971713168109</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.04130768847402259</v>
+        <v>0.07557136892713842</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.05823925304369246</v>
+        <v>-0.1639315420293525</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0.01261547495367103</v>
+        <v>0.2229533763812394</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.08187283595888863</v>
+        <v>0.427052589431358</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01788595156896632</v>
+        <v>0.06888495513807723</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.03619966431532144</v>
+        <v>-0.2604138337548567</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02616505401158302</v>
+        <v>0.1888230147314818</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,25 +2745,25 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.007472454984637081</v>
+        <v>-0.02988036452346332</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.02396280479498232</v>
+        <v>-0.1962992511303498</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>-0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00623493929843797</v>
+        <v>0.1197437404470144</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.003810217957325646</v>
+        <v>-0.1158367847424722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.005935103970945353</v>
+        <v>-0.06226868495683641</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,91 +2787,91 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01570567996040501</v>
+        <v>-0.03478879304087922</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02005423544544419</v>
+        <v>-0.2375399588328306</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.002577763039957782</v>
+        <v>0.08597232482224741</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01212467331209952</v>
+        <v>0.1971506754993267</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01170179461750233</v>
+        <v>0.1222677545083017</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.01695411866153231</v>
+        <v>-0.1494247770424625</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0819182185973497</v>
+        <v>0.4245624060856026</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.01069360534639153</v>
+        <v>-0.1961330952947217</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.00245863163269701</v>
+        <v>-0.1226008536927913</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02862710770225349</v>
+        <v>0.03865239061328517</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.03031103844955549</v>
+        <v>-0.02530537993775285</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.06499869683216976</v>
+        <v>-0.1116814633676528</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.02674952219401873</v>
+        <v>-0.006761962615377087</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02412277475503327</v>
+        <v>0.09649894760460921</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.003455965408192872</v>
+        <v>0.1609622699610709</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.03320446831974715</v>
+        <v>0.3271443645820599</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,37 +2934,37 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0004176975673064586</v>
+        <v>-0.03108214526084902</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.0133706109728433</v>
+        <v>-0.3230195981487131</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.01987442859308093</v>
+        <v>-0.2231465428330222</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0009020345195736598</v>
+        <v>-0.05191723940243462</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0259724256499671</v>
+        <v>0.2057164385019232</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01184285293752544</v>
+        <v>-0.1454833694244511</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
@@ -2988,97 +2988,97 @@
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.01616715470987497</v>
+        <v>0.1597212277193165</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.00263718248814179</v>
+        <v>0.004770952969204864</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.01441434160121328</v>
+        <v>-0.2004732084439343</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.002030277521816523</v>
+        <v>-0.01439218189707167</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.02659902297599469</v>
+        <v>0.2185884486424339</v>
       </c>
       <c r="DB5" t="n">
         <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.001044153881051279</v>
+        <v>-0.0614322181150342</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02796570389473694</v>
+        <v>-0.09230466057271666</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.005933870741451377</v>
+        <v>0.05318946842092692</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.006889662996651101</v>
+        <v>-0.1000933232073465</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.001992156146441421</v>
+        <v>0.02999678846540567</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.006657918363706377</v>
+        <v>-0.0006162350855341734</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,46 +3087,46 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01290068023462178</v>
+        <v>0.02436447782064815</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03185858114901458</v>
+        <v>0.009891965597558422</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.002177194120003404</v>
+        <v>0.1475833578516315</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.02315874160745404</v>
+        <v>-0.07988988507190725</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.01004180724135467</v>
+        <v>-0.109993919742503</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.02268967723294838</v>
+        <v>0.0931288622213288</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3138,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.01265435205936193</v>
+        <v>-0.1700978788387084</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02299118076957868</v>
+        <v>-0.1434689457254692</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01191818864676632</v>
+        <v>0.07224611081412392</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.01721876809764708</v>
+        <v>-0.2155422387844038</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,25 +3177,25 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.003716960047084964</v>
+        <v>-0.06863235589276906</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.02483343750746227</v>
+        <v>0.1907338862781412</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.00854343257363065</v>
+        <v>-0.1875157581812032</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,25 +3204,25 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.03677164741241872</v>
+        <v>0.03528107243319159</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01912191582811358</v>
+        <v>0.2940542199349072</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.003579621120260352</v>
+        <v>-0.02120548199293019</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
@@ -3231,46 +3231,46 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.000492496695095602</v>
+        <v>-0.005557967352782384</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0145479937270314</v>
+        <v>0.1221233271785424</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02941631913428946</v>
+        <v>-0.126745489682096</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.01389649846273062</v>
+        <v>0.1566987075979966</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
         <v>0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1713794130513188</v>
+        <v>0.4163013630837659</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01892467161469861</v>
+        <v>0.0637892423177354</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.109753902884278</v>
+        <v>-0.2472880162345608</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
@@ -3305,25 +3305,25 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07570235766345126</v>
+        <v>0.2454196476887101</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.007635398579040155</v>
+        <v>-0.01528886888687996</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.07252769621602427</v>
+        <v>-0.1665620716945222</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -3332,49 +3332,49 @@
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02509258889074246</v>
+        <v>0.1003798009426553</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01181035028821421</v>
+        <v>-0.1265249537302391</v>
       </c>
       <c r="X6" t="n">
-        <v>0.008440540590872351</v>
+        <v>-0.04904535052386507</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02894888915720263</v>
+        <v>0.04797050750544034</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0226366252413698</v>
+        <v>-0.2720323117929496</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.006725632341609495</v>
+        <v>-0.09576204333432033</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.04003063297870788</v>
+        <v>0.1564840423920686</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.00591294617959779</v>
+        <v>0.1258633893889815</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.04255940749882337</v>
+        <v>-0.09757028629236213</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,22 +3410,22 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1418616465296543</v>
+        <v>0.3753269637478224</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0004032753216122987</v>
+        <v>-0.107539184748029</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.05720184750516601</v>
+        <v>-0.156561142967334</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.06345228374218279</v>
+        <v>0.06288102379200017</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,40 +3449,40 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.05110581130623398</v>
+        <v>-0.07538719127855485</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.09164535468444025</v>
+        <v>-0.2077626148106253</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04291401818358646</v>
+        <v>-0.03818633829937407</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02136770651641674</v>
+        <v>0.09608036656174403</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.004147470016605554</v>
+        <v>0.03268761960945283</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>0</v>
@@ -3491,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.07180169613644215</v>
+        <v>0.2588734349204948</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.004625417700504807</v>
+        <v>0.01632068332684056</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.02228143168241953</v>
+        <v>-0.1649953519156355</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>-0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.04383624029890307</v>
+        <v>-0.21103185572465</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.005633421692239364</v>
+        <v>-0.05432542109644117</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.04490986007188176</v>
+        <v>0.1617830925892925</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,49 +3548,49 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.02844427109563514</v>
+        <v>-0.1833681650334029</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.003542627802623093</v>
+        <v>0.1049442979737943</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01438444263170192</v>
+        <v>0.06171293137598962</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.0356239483984902</v>
+        <v>-0.1943251126012025</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.002536505210310589</v>
+        <v>-0.04370780074094443</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.04775367435203452</v>
+        <v>0.1601517766153501</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
@@ -3599,22 +3599,22 @@
         <v>-0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01726078474621639</v>
+        <v>-0.05731713028794062</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.009889988242547873</v>
+        <v>-0.06382608921997072</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-1.313835936353034e-06</v>
+        <v>0.01313982555810845</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,52 +3623,52 @@
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.01363236212848895</v>
+        <v>-0.07520010427630841</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.009784955756976998</v>
+        <v>-0.03915647259582208</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.02486892102637919</v>
+        <v>0.1005175199334114</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.01269912638380186</v>
+        <v>0.05270455561640774</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.03250054760888751</v>
+        <v>0.1445425600997494</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0004203229311097074</v>
+        <v>0.1075747050669932</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
@@ -3677,13 +3677,13 @@
         <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0295166063685969</v>
+        <v>-0.07887191442190997</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
@@ -3692,37 +3692,37 @@
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.003453209687453299</v>
+        <v>-0.05002772571432287</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.03657371726072015</v>
+        <v>0.06291907382106379</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.02932533213330311</v>
+        <v>-0.1053848230801172</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01289750679968222</v>
+        <v>-0.06391137910081489</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03688696515449237</v>
+        <v>0.1332808993998914</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3737,100 +3737,100 @@
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.03921657459231797</v>
+        <v>-0.2157491886113656</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.002965518598960173</v>
+        <v>-0.07649341808527116</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.04395900847001553</v>
+        <v>0.1369631305354479</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.0238715624459405</v>
+        <v>-0.2368003006071017</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02218599795578857</v>
+        <v>0.05979007135881167</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02129309600338048</v>
+        <v>0.2440998620821875</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.008810360560574477</v>
+        <v>-0.03728713676664267</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001772533131612066</v>
+        <v>-0.01271272480923539</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.02761802697644911</v>
+        <v>0.1759317624078174</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.0402653915063716</v>
+        <v>-0.08117253687951441</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.005833040448543275</v>
+        <v>0.0380803942864549</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -4416,73 +4416,73 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3926886793102888</v>
+        <v>0.5728493218581501</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1365453942531331</v>
+        <v>-0.02316910232058339</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06135052049214819</v>
+        <v>0.1684222876427434</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08908102656207099</v>
+        <v>-0.1783125835493362</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2477188306347894</v>
+        <v>0.4747245057798334</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09609608700566104</v>
+        <v>-0.1406453512985731</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.04287203157107024</v>
+        <v>0.02838114477140138</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.06923070025032288</v>
+        <v>-0.09559565293531448</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06018502757474238</v>
+        <v>0.09025516687903821</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.01756942906524828</v>
+        <v>-0.1161722212131781</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05223183262016945</v>
+        <v>-0.09843164846899728</v>
       </c>
       <c r="X8" t="n">
-        <v>0.05167334577581594</v>
+        <v>0.01429188152017097</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
@@ -4491,79 +4491,79 @@
         <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.02330185984541077</v>
+        <v>0.0585843325243075</v>
       </c>
       <c r="AD8" t="n">
         <v>-0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.1150661501378136</v>
+        <v>-0.3228442699951608</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.04131269553359647</v>
+        <v>-0.1888373914900777</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.0227997950559226</v>
+        <v>-0.09623712470755073</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01456182233038986</v>
+        <v>0.2250689299493236</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.02655612931762007</v>
+        <v>-0.1322039286245605</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0003339925803306597</v>
+        <v>0.1500259014805911</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.06404570946564596</v>
+        <v>-0.1643462535804428</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3949963039240794</v>
+        <v>0.377247054239745</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.02230098382110633</v>
+        <v>-0.002904194119691591</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1110132249620883</v>
+        <v>-0.06816111981994639</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.1573292114618001</v>
+        <v>-0.05717149119248359</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4572,139 +4572,139 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.04746907816803728</v>
+        <v>0.1186885011221514</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.01758874989933211</v>
+        <v>-0.07837867354795856</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.08495922417927249</v>
+        <v>-0.06953089388861047</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.2488031012363983</v>
+        <v>-0.2543458355834692</v>
       </c>
       <c r="BI8" t="n">
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0279798122837994</v>
+        <v>-0.02622202447111404</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.04682831504218452</v>
+        <v>0.02855432247110774</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.09615459817458288</v>
+        <v>0.1088487747586574</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0278144360465245</v>
+        <v>-0.04061956360088784</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1800357826400644</v>
+        <v>0.2670520342296812</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.03944476423870449</v>
+        <v>-0.04984882113586914</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.01000190164614114</v>
+        <v>0.04778544408191692</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.09790758714660468</v>
+        <v>-0.1490753176989521</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
         <v>-0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.08489435563096837</v>
+        <v>-0.2321271674363351</v>
       </c>
       <c r="CF8" t="n">
         <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.01528869399273533</v>
+        <v>0.05814608127066674</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.01707767930938972</v>
+        <v>-0.09311265661915988</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04539655343499202</v>
+        <v>0.09465313587086642</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.07668827123582143</v>
+        <v>-0.1896670097009751</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.1022154187547283</v>
+        <v>0.172793537928213</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.1500050748572051</v>
+        <v>0.01056488137018382</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.07213995445446381</v>
+        <v>0.1987106019627524</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
@@ -4713,79 +4713,79 @@
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.08256465873710113</v>
+        <v>-0.2153851866124845</v>
       </c>
       <c r="CX8" t="n">
         <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.04040560023108161</v>
+        <v>0.05042760695137731</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.002263642318322425</v>
+        <v>-0.09630861405790392</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.07585906650282848</v>
+        <v>0.08647789470379975</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.01275571396523019</v>
+        <v>-0.03052032145298217</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1263675657751716</v>
+        <v>-0.03038447053017059</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.01369112019809822</v>
+        <v>0.4493923588640402</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.007468728881301961</v>
+        <v>0.01327266479580302</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.06867300415538784</v>
+        <v>-0.1256286574051897</v>
       </c>
       <c r="DP8" t="n">
         <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.008175238108033611</v>
+        <v>-0.004097513175068141</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.01049258639422003</v>
+        <v>-0.08174642613319469</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.04623288677949244</v>
+        <v>0.1572818369634406</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>-0</v>
@@ -4794,130 +4794,130 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.02619485015428234</v>
+        <v>0.08893983879043367</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.01401742328717328</v>
+        <v>0.07817733106716732</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.03594607381291359</v>
+        <v>0.07470954741901341</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.05034925057673755</v>
+        <v>0.005245355839063063</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.1385310962453149</v>
+        <v>-0.0885099223700038</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.08792786857933774</v>
+        <v>0.09231624335961133</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.09716257225126976</v>
+        <v>-0.09638404542959625</v>
       </c>
       <c r="EK8" t="n">
-        <v>-0.002308214746918405</v>
+        <v>-0.04250510780774819</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.07443717235647483</v>
+        <v>-0.07936674026230627</v>
       </c>
       <c r="EQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>-0.01958275743200161</v>
+        <v>-0.07813824821281322</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.007398505192010304</v>
+        <v>-0.06166969781138453</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.1180046043719705</v>
+        <v>0.2205040129443227</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.07640412963521893</v>
+        <v>-0.2387490207095108</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.009948831104005032</v>
+        <v>0.05215603190380939</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.009159389543222717</v>
+        <v>-0.132039859456497</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.05048918996764769</v>
+        <v>0.06135551339702408</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
         <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.05737526836358202</v>
+        <v>-0.2130312145997908</v>
       </c>
       <c r="FI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.05655793629884794</v>
+        <v>0.09098150561242126</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.01879917378061038</v>
+        <v>-0.0459195105259602</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.006229051207426107</v>
+        <v>0.3147877925109819</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
         <v>0</v>
@@ -4926,58 +4926,58 @@
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.001531620594227596</v>
+        <v>-0.175139329736296</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>-0.0551834309710118</v>
+        <v>0.2462044687342726</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.006999546615907364</v>
+        <v>-0.01846024841494691</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0.03731120619640287</v>
+        <v>0.07563413192255782</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
         <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.1103519676567491</v>
+        <v>-0.09953277050853712</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.06948476771907966</v>
+        <v>-0.1687395677815061</v>
       </c>
       <c r="GC8" t="n">
         <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.00183617494813954</v>
+        <v>-0.07336780270775875</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
         <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5554,7 +5554,7 @@
         <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.5283914224206286</v>
+        <v>-0.258140792146666</v>
       </c>
       <c r="C10" t="n">
         <v>-0</v>
@@ -5563,13 +5563,13 @@
         <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003147124462677014</v>
+        <v>-0.03805504813317089</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7282964234395957</v>
+        <v>0.2183172581347803</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5581,7 +5581,7 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2576220748438526</v>
+        <v>-0.1574975212321034</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,13 +5590,13 @@
         <v>-0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.08755258539904424</v>
+        <v>0.02142523106538924</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4954912584070811</v>
+        <v>0.132293092154696</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -5608,34 +5608,34 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.05287625667856224</v>
+        <v>-0.07382843509467975</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>-0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.09266587989764534</v>
+        <v>0.007468019473238224</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02503722379902499</v>
+        <v>-0.04341671024639879</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.09196414565272197</v>
+        <v>0.05431291315334905</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
@@ -5644,10 +5644,10 @@
         <v>-0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.003562138555045154</v>
+        <v>0.09719154517609328</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.1654812931005469</v>
+        <v>0.03612195410265724</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5656,28 +5656,28 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.07840102353032</v>
+        <v>-0.1013585123095763</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1139179025692985</v>
+        <v>-0.09359533538297837</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.1983817922103623</v>
+        <v>0.1472715750013164</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5686,22 +5686,22 @@
         <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.2383644404061573</v>
+        <v>-0.2050086854713133</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.02937140010255998</v>
+        <v>-0.007232803318388428</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.3236518652441142</v>
+        <v>0.07027207347606086</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
@@ -5710,13 +5710,13 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.2039539909957105</v>
+        <v>0.1008775135033718</v>
       </c>
       <c r="BE10" t="n">
         <v>-0</v>
@@ -5725,10 +5725,10 @@
         <v>-0</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.106097143754319</v>
+        <v>0.2202663725209223</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.2599298027329151</v>
+        <v>0.1583261224195202</v>
       </c>
       <c r="BI10" t="n">
         <v>0</v>
@@ -5737,13 +5737,13 @@
         <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.05540406911458669</v>
+        <v>0.03077073923596566</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -5752,10 +5752,10 @@
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.07780748520141645</v>
+        <v>-0.06290647155380348</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0.01927262277726467</v>
+        <v>-0.0544768063576443</v>
       </c>
       <c r="BR10" t="n">
         <v>0</v>
@@ -5767,28 +5767,28 @@
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.2002768644924784</v>
+        <v>-0.2206411636604803</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.005133123227497339</v>
+        <v>-0.02731194740787286</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.1687152589357802</v>
+        <v>0.06690452190431226</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.1284504385197967</v>
+        <v>0.1255800390089049</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
@@ -5806,37 +5806,37 @@
         <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.001700276050467914</v>
+        <v>0.009947908732685974</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0.1318672845489291</v>
+        <v>-0.07703142146543009</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK10" t="n">
         <v>-0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.02880937887162975</v>
+        <v>0.1273687834910905</v>
       </c>
       <c r="CO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1581050339349822</v>
+        <v>-0.1448701432728961</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1112392202815619</v>
+        <v>-0.06881209473811666</v>
       </c>
       <c r="CS10" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1002005632381933</v>
+        <v>0.120504614536831</v>
       </c>
       <c r="CX10" t="n">
         <v>-0</v>
@@ -5860,13 +5860,13 @@
         <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.02632988616287044</v>
+        <v>0.0150142573808593</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0.1721105843893959</v>
+        <v>-0.07127625096449977</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
         <v>0</v>
@@ -5875,55 +5875,55 @@
         <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.006623522347681468</v>
+        <v>-0.001613814266967102</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
         <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.2065532395227702</v>
+        <v>0.07239667204417014</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.04110858911518869</v>
+        <v>-0.008372324857505149</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.09845532003294798</v>
+        <v>0.0180268171160097</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.004892756027968412</v>
+        <v>0.02227129347450661</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.02624013931227699</v>
+        <v>-0.01776074443963779</v>
       </c>
       <c r="DT10" t="n">
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,19 +5932,19 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.01452186640111653</v>
+        <v>-0.01526327740550702</v>
       </c>
       <c r="DY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.1947998699956032</v>
+        <v>0.003978996816165556</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.02671693506866205</v>
+        <v>-0.003744672605795268</v>
       </c>
       <c r="EC10" t="n">
         <v>0</v>
@@ -5953,25 +5953,25 @@
         <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.07739903866462014</v>
+        <v>0.05528337786714893</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.05333012070582895</v>
+        <v>0.002561250545995584</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0.1432692400093165</v>
+        <v>0.007628251948789913</v>
       </c>
       <c r="EL10" t="n">
         <v>0</v>
@@ -5980,13 +5980,13 @@
         <v>0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.155510776297217</v>
+        <v>0.104540059945624</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,25 +5995,25 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.02806994949283125</v>
+        <v>0.094165900068058</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.1275767779425557</v>
+        <v>0.1132506239384272</v>
       </c>
       <c r="EU10" t="n">
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
         <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1199080643387139</v>
+        <v>0.1354328702019889</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
@@ -6022,13 +6022,13 @@
         <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.02186956206601598</v>
+        <v>0.0286477217021317</v>
       </c>
       <c r="FC10" t="n">
-        <v>-0.1634322186791656</v>
+        <v>-0.05942317094630237</v>
       </c>
       <c r="FD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE10" t="n">
         <v>-0</v>
@@ -6037,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.01211649542923368</v>
+        <v>0.1358731400650176</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,37 +6049,37 @@
         <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.06753624719041072</v>
+        <v>-0.03443629821388391</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0.06475994080631081</v>
+        <v>-0.08237897300295552</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.06385377685465279</v>
+        <v>0.1256390609460321</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.05209973275440163</v>
+        <v>0.01800913072830964</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.1531211471075874</v>
+        <v>-0.05092330247656154</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
@@ -6088,16 +6088,16 @@
         <v>-0</v>
       </c>
       <c r="FX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY10" t="n">
         <v>-0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.1665781732194213</v>
+        <v>0.1043774997360905</v>
       </c>
       <c r="GA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB10" t="n">
         <v>0</v>
@@ -6106,24 +6106,24 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.05113894467898045</v>
+        <v>0.01797403074479533</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF10" t="n">
         <v>0</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2516065355562112</v>
+        <v>0.4520557892259223</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01869473350911864</v>
+        <v>0.03456075394403511</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1620592924349578</v>
+        <v>-0.2101389893434686</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6147,28 +6147,28 @@
         <v>-0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.194503247676321</v>
+        <v>0.502223904833199</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02220989086086562</v>
+        <v>-0.05531711829093226</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1211956380578382</v>
+        <v>-0.13868057764636</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
@@ -6177,25 +6177,25 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0277144771957759</v>
+        <v>0.1007918269783607</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01992651293359777</v>
+        <v>0.037546747422199</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01467480711689152</v>
+        <v>-0.08930275524047178</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,19 +6204,19 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03202216902423068</v>
+        <v>-0.03443189822730471</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01420845947731902</v>
+        <v>-0.04421287495046387</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01575746823512983</v>
+        <v>0.05063154446230544</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -6231,19 +6231,19 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0280171460500328</v>
+        <v>0.1419587004808787</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02418728249508569</v>
+        <v>0.06673486568037056</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.06865145237668588</v>
+        <v>-0.08636158650444462</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -6255,37 +6255,37 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1550150551983126</v>
+        <v>0.3461719967271588</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.02665833060427253</v>
+        <v>-0.1204677369278234</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.06532045777545753</v>
+        <v>-0.1156099693105943</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.08349232001166544</v>
+        <v>-0.09947133744484943</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,13 +6294,13 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.06312899480197592</v>
+        <v>-0.02387081338859272</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.09233573397660733</v>
+        <v>-0.05252665343020513</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
         <v>-0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.07542215848354106</v>
+        <v>-0.03933696626165624</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0302527361786107</v>
+        <v>0.07558797924124709</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.04035458844157969</v>
+        <v>0.04682952444057187</v>
       </c>
       <c r="BR11" t="n">
         <v>-0</v>
@@ -6336,10 +6336,10 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1053516172500136</v>
+        <v>0.3057764213378974</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,13 +6348,13 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.02287628520274828</v>
+        <v>0.03247580741484916</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.03316472666585606</v>
+        <v>-0.1005974954038188</v>
       </c>
       <c r="CA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="n">
         <v>-0</v>
@@ -6366,25 +6366,25 @@
         <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.05136423788707088</v>
+        <v>-0.1771663559165564</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.009789880049820081</v>
+        <v>-0.00609585160971118</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.03659045480511312</v>
+        <v>0.06469817149102677</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
         <v>0</v>
@@ -6393,61 +6393,61 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.04110894318229944</v>
+        <v>-0.0631858312174234</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.03163966403172979</v>
+        <v>0.07782460821284376</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.02140388949232277</v>
+        <v>0.02231099438743359</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.03724984259746821</v>
+        <v>-0.1708622325329142</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.007195036978348065</v>
+        <v>0.004314431746440945</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.04415952137769032</v>
+        <v>0.07698775191264162</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.005643708400773112</v>
+        <v>0.01275259230995918</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.005184475568263673</v>
+        <v>0.01904889328640628</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01252524204076916</v>
+        <v>0.07711215964987315</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6474,25 +6474,25 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.01907523311533118</v>
+        <v>-0.06534684424160081</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.001556273477890819</v>
+        <v>-0.03448563199484778</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.01084237679480029</v>
+        <v>0.08918764447824198</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,46 +6501,46 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.05767496116426071</v>
+        <v>-0.09330410075664919</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01073957232190554</v>
+        <v>0.01798154046620131</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.03443815800016475</v>
+        <v>-0.1039160018485603</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.02942373276540911</v>
+        <v>-0.122437560000968</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.002565719896306367</v>
+        <v>-0.03388878263194535</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01978182389262372</v>
+        <v>0.008107569612124549</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6555,19 +6555,19 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.00302666132268416</v>
+        <v>0.101149024211521</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.01131280024313108</v>
+        <v>-0.01280796359485258</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.008900233666226217</v>
+        <v>-0.05004057310745948</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
@@ -6576,40 +6576,40 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.03863928362347025</v>
+        <v>-0.1893257203229719</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.001461288147201411</v>
+        <v>-0.02430235023055738</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.04607969545788086</v>
+        <v>0.07812635416473987</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.005840626453025755</v>
+        <v>-0.07510952752552438</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,10 +6618,10 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02663366389764812</v>
+        <v>-0.006453816610237238</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.04152876669864391</v>
+        <v>0.05381887551191859</v>
       </c>
       <c r="FM11" t="n">
         <v>-0</v>
@@ -6636,7 +6636,7 @@
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.02575910869704859</v>
+        <v>-0.1420056129684883</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.03991647730728398</v>
+        <v>-0.07943537927208313</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.00292809167061851</v>
+        <v>-0.004365840687855565</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.03193951623530966</v>
+        <v>-0.1200301307331278</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.06445939264966975</v>
+        <v>0.05055889510967777</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,16 +6692,16 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>2.0406385542872</v>
+        <v>0.942033124171857</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8902476184013699</v>
+        <v>-0.5593338693329744</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.140550154303724</v>
+        <v>0.1057953746245108</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6713,22 +6713,22 @@
         <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>1.640834696714954</v>
+        <v>1.036217214173179</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7428088079253242</v>
+        <v>-0.813076122074982</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.991343862332668</v>
+        <v>-0.05061500916165637</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6737,34 +6737,34 @@
         <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4781658061839918</v>
+        <v>0.0459652754349123</v>
       </c>
       <c r="U12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1275600108175528</v>
+        <v>0.002562654190542511</v>
       </c>
       <c r="W12" t="n">
-        <v>0.00148447910802298</v>
+        <v>-0.002958598686084093</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,22 +6773,22 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.5368668954180984</v>
+        <v>0.2456238819456928</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.09545000168913126</v>
+        <v>-0.3512942007857721</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.1447758597609176</v>
+        <v>0.4878523461516559</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,25 +6797,25 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.3666843451312236</v>
+        <v>0.3115693531611036</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.03872985032320367</v>
+        <v>-0.2022147271099475</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.1813800919471867</v>
+        <v>0.3542200142241567</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -6827,25 +6827,25 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.24526468127957</v>
+        <v>0.5302024446652119</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.1535194345200939</v>
+        <v>-0.367986388220801</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.3345061557355587</v>
+        <v>-0.2189978619805212</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,19 +6854,19 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.333184670328357</v>
+        <v>0.04621397371194979</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.4395436923720483</v>
+        <v>0.04259938496904454</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.886943238672714</v>
+        <v>0.1578198071095767</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
@@ -6881,16 +6881,16 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.349752365550903</v>
+        <v>-0.1217320767655218</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.1212027235579398</v>
+        <v>-0.1280502957929714</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1541991282872415</v>
+        <v>-0.02847447851869223</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6899,52 +6899,52 @@
         <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.9317630051163499</v>
+        <v>0.2195065912553192</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.02399061556935784</v>
+        <v>-0.2524993104211428</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.2952951972369489</v>
+        <v>-0.1144909304210448</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.4485944247333926</v>
+        <v>-0.3815411382489773</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.1567581340838901</v>
+        <v>0.2446736402616103</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.1009794670475838</v>
+        <v>-0.07340305837576307</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6962,76 +6962,76 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.1220484377591267</v>
+        <v>-0.12992707218459</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.03862535848932194</v>
+        <v>0.358392466274654</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.345814913071178</v>
+        <v>0.1178172439691247</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV12" t="n">
         <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.3813287026966577</v>
+        <v>-0.3707567451943721</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.2482959826666862</v>
+        <v>0.2451309087730826</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.03302122348503764</v>
+        <v>0.006966209683260267</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.4937506032084342</v>
+        <v>-0.3039868846282459</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.4271097881272007</v>
+        <v>0.08268672333727278</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.002437462429212044</v>
+        <v>-0.01758415516543218</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7040,19 +7040,19 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.2756957416844208</v>
+        <v>-0.06228205341454698</v>
       </c>
       <c r="DP12" t="n">
         <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.1743360711249024</v>
+        <v>0.2171616444658958</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.1592169641431032</v>
+        <v>-0.1551223427816312</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
@@ -7070,22 +7070,22 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.1956765083416818</v>
+        <v>-0.1531134017568644</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.1575018148302079</v>
+        <v>-0.04270332507050537</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.2429281178187477</v>
+        <v>0.1162811029084531</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7097,46 +7097,46 @@
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.3240996522032035</v>
+        <v>-0.4117491934824616</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.1327572795094883</v>
+        <v>0.2018648437118453</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.3313237395681666</v>
+        <v>0.03462089780759708</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.09072804987080889</v>
+        <v>0.2144448697610454</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.2397064038302912</v>
+        <v>0.07860238912316342</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.08268389677316298</v>
+        <v>0.03175001514206573</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
@@ -7151,43 +7151,43 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.3709003077989703</v>
+        <v>-0.4341133176842613</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.2481074472495689</v>
+        <v>0.2815702928020501</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.04128431917975884</v>
+        <v>-0.07598776906855446</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.1631970748280745</v>
+        <v>-0.2216853497924461</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>-0.3455343103978719</v>
+        <v>-0.2166999825431294</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01400248371133362</v>
+        <v>-0.1905426649668845</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7199,58 +7199,58 @@
         <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.1090188335561572</v>
+        <v>-0.333791741342524</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.05992833630196636</v>
+        <v>-0.02652223655791431</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.04758727323510854</v>
+        <v>0.08623337533603563</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.02571918467818198</v>
+        <v>-0.261936947948267</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.09128693519641287</v>
+        <v>0.06889651767209144</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7258,79 +7258,79 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>2.302078055914711</v>
+        <v>-0.8105446945223669</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2517215424330436</v>
+        <v>0.3695367444688021</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.642013459313908</v>
+        <v>0.9266834946935657</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.023164522400701</v>
+        <v>-1.027774472690889</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.05383206320594003</v>
+        <v>0.9948500001145798</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.139449688339426</v>
+        <v>1.072608347988826</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1448423965361824</v>
+        <v>-0.2097742331867797</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.2750479477819067</v>
+        <v>0.2155339525858154</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3798503599255162</v>
+        <v>0.101792878415913</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -7339,82 +7339,82 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.363959018515035</v>
+        <v>-0.2035341649454092</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.07396618341370964</v>
+        <v>0.3387555186810312</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.2379841760846622</v>
+        <v>0.2118069087914383</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.2100189781704509</v>
+        <v>-0.2797123661984626</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.419054032055011</v>
+        <v>-0.1150549919859286</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.579037165353103</v>
+        <v>0.1683807273889118</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.164276814495944</v>
+        <v>-1.30530506597464</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.02992575846060882</v>
+        <v>0.1270686891959825</v>
       </c>
       <c r="AY13" t="n">
-        <v>-1.763501115544519</v>
+        <v>0.5920901711258429</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
@@ -7423,46 +7423,46 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.6271063789268441</v>
+        <v>0.6644006689364441</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.5615168125330545</v>
+        <v>0.3403409198929309</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.6105721187876442</v>
+        <v>0.05851646655997121</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
         <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.4752099098414173</v>
+        <v>-0.2236746074337476</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.004174835902408049</v>
+        <v>-0.2629699869456639</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0.1999234212487693</v>
+        <v>-0.1691276547310148</v>
       </c>
       <c r="BR13" t="n">
         <v>-0</v>
@@ -7471,13 +7471,13 @@
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.8586088475327155</v>
+        <v>-0.7111234667030464</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,52 +7486,52 @@
         <v>-0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.1051437488393054</v>
+        <v>0.2504089013490798</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.8607299812160878</v>
+        <v>0.2916549838507738</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.4867844363945717</v>
+        <v>0.2926486969014712</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.03293254953194606</v>
+        <v>-0.2002679188218852</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.3431947654819701</v>
+        <v>-0.243566860047396</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
       </c>
       <c r="CK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.1375599189491589</v>
+        <v>0.2502694153406907</v>
       </c>
       <c r="CO13" t="n">
         <v>0</v>
@@ -7540,67 +7540,67 @@
         <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.2536922919140927</v>
+        <v>-0.2939640800930391</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.1281031196870485</v>
+        <v>-0.1325863711994382</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.4048719237502993</v>
+        <v>0.2693530256430743</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.04694836840359604</v>
+        <v>-0.2085143320053161</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.3858428291605034</v>
+        <v>-0.3096367352030023</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.5400829612092838</v>
+        <v>0.2646905492432633</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.4354261881522185</v>
+        <v>0.3638616013888032</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.5906206839656081</v>
+        <v>-0.2617662332814833</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
@@ -7612,19 +7612,19 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.2165078669639293</v>
+        <v>-0.1792780130152736</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.06950714016777096</v>
+        <v>0.1366808932818654</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.3393828130595613</v>
+        <v>-0.2044346395673819</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
@@ -7633,31 +7633,31 @@
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.2086088051878926</v>
+        <v>0.3552120903107229</v>
       </c>
       <c r="DY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.1285140390942495</v>
+        <v>-0.09745956571726488</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.2975907491264709</v>
+        <v>-0.01367379507384383</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE13" t="n">
         <v>0</v>
@@ -7666,7 +7666,7 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.3560148420983008</v>
+        <v>0.1796089692993806</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,10 +7675,10 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.237363827241719</v>
+        <v>-0.2314330529233885</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.03222591069220682</v>
+        <v>0.1460672824307986</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7690,25 +7690,25 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.2890518237526165</v>
+        <v>-0.1720294264169833</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.2479209837516308</v>
+        <v>0.06105567783783522</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0.1660989616007269</v>
+        <v>-0.243559093634786</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7717,49 +7717,49 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.4041441315643215</v>
+        <v>0.3274009667100357</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.01107567692722042</v>
+        <v>-0.1443185325370427</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.3356417156421466</v>
+        <v>-0.2708438029303122</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
         <v>0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.1113655289363883</v>
+        <v>0.2266691597700384</v>
       </c>
       <c r="FI13" t="n">
         <v>0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.05005242953781455</v>
+        <v>-0.07813844026286704</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.3166951956505472</v>
+        <v>-0.2153591150034226</v>
       </c>
       <c r="FM13" t="n">
         <v>-0</v>
@@ -7768,40 +7768,40 @@
         <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.1641193736210981</v>
+        <v>0.06810458706821823</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.4440372414835626</v>
+        <v>-0.3747230123368007</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.4133376030149396</v>
+        <v>0.1559555698259053</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
         <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.1572051969257538</v>
+        <v>-0.01574046848390195</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.3194260776214765</v>
+        <v>-0.003168258962409513</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
         <v>0</v>
@@ -7827,73 +7827,73 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.5599100438199569</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1.050020863819467</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3147245161396676</v>
+        <v>-0</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.448027549541633</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7400365403683685</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.272684590709271</v>
+        <v>-0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1918193957326597</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.130336764980623</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1900164385804097</v>
+        <v>-0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -7902,82 +7902,82 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.06021481104608277</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0969145910042586</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.03121996576819917</v>
+        <v>-0</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.1633949443435726</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.06545632349004307</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.07665280662361823</v>
+        <v>-0</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.3048409136725442</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.4295557371874041</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1069280712115607</v>
+        <v>-0</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -7986,31 +7986,31 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.1852514544884164</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.4310814736176468</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.2826310010798516</v>
+        <v>-0</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
@@ -8019,22 +8019,22 @@
         <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.1747123649364067</v>
+        <v>0</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.02634827879058006</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.2040868279756383</v>
+        <v>-0</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
@@ -8046,16 +8046,16 @@
         <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.1988621796236317</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.1679921707871132</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.04929734368925874</v>
+        <v>-0</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -8067,52 +8067,52 @@
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
         <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.09397256753552523</v>
+        <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.1878812690494974</v>
+        <v>0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01035293738019606</v>
+        <v>-0</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.03180443459335135</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
         <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0003027418749707973</v>
+        <v>0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.1003744779270384</v>
+        <v>-0</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS14" t="n">
         <v>0</v>
@@ -8121,49 +8121,49 @@
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.08226409372898431</v>
+        <v>0</v>
       </c>
       <c r="CX14" t="n">
         <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.2076550669469801</v>
+        <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.03443710150081503</v>
+        <v>0</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.1881454475770754</v>
+        <v>0</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.3240493412344442</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.2931670465828338</v>
+        <v>-0</v>
       </c>
       <c r="DJ14" t="n">
         <v>0</v>
@@ -8172,28 +8172,28 @@
         <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.009292538777876348</v>
+        <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.03831390796173454</v>
+        <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.09960777875463489</v>
+        <v>-0</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT14" t="n">
         <v>0</v>
@@ -8202,49 +8202,49 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.07810678308341908</v>
+        <v>0</v>
       </c>
       <c r="DY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.09673662653469002</v>
+        <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.001765021540908611</v>
+        <v>-0</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0716577644725838</v>
+        <v>0</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.1254035912057079</v>
+        <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.1317925914482092</v>
+        <v>0</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
@@ -8262,25 +8262,25 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.04657785520115242</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.01411790966509287</v>
+        <v>0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.002714522490093503</v>
+        <v>-0</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
         <v>0</v>
@@ -8289,16 +8289,16 @@
         <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.08183265230553262</v>
+        <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.1804853189987381</v>
+        <v>0</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.03831643761185867</v>
+        <v>-0</v>
       </c>
       <c r="FC14" t="n">
         <v>0</v>
@@ -8307,25 +8307,25 @@
         <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.05835631089210017</v>
+        <v>0</v>
       </c>
       <c r="FI14" t="n">
         <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>-0.1933783790294422</v>
+        <v>0</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.004935912850177751</v>
+        <v>-0</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
@@ -8337,22 +8337,22 @@
         <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP14" t="n">
         <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.03199625284883757</v>
+        <v>0</v>
       </c>
       <c r="FR14" t="n">
         <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.151420881489206</v>
+        <v>0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.2233925918086138</v>
+        <v>-0</v>
       </c>
       <c r="FU14" t="n">
         <v>0</v>
@@ -8364,22 +8364,22 @@
         <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
         <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.1538941175194398</v>
+        <v>0</v>
       </c>
       <c r="GA14" t="n">
         <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.07838252429901899</v>
+        <v>0</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
         <v>0</v>
@@ -8388,1147 +8388,9 @@
         <v>0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>0</v>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.4694112603714919</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.2710339508115251</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.7397930556924082</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.4346483387182067</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.1173725285455399</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.5972556050245771</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-0.05198071134366324</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.1015416820210057</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.0297516703088462</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>-0.1118550111766569</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.06516019077510581</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>-0.01739232010157258</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>-0.1132070176150761</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>-0.09089700390295564</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.1739261636790081</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>-0.3496899527718045</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0.09276502183887261</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0.5438418323079567</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>-0.1074494346709868</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0.2338965409089844</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>0.1387182181878182</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>-0.2046965199291179</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>-0.01817155673899798</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>0.00890812982570072</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>-0.2487398972275829</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>0.06934243574014651</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>0.2193850586957588</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE15" t="n">
-        <v>0.08685139991679428</v>
-      </c>
-      <c r="CF15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH15" t="n">
-        <v>-0.03769286755693406</v>
-      </c>
-      <c r="CI15" t="n">
-        <v>-0.1234789907323716</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>0.004223502285298179</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>-0.0952541723043958</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>0.0313220297290467</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW15" t="n">
-        <v>0.06445553443237705</v>
-      </c>
-      <c r="CX15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CZ15" t="n">
-        <v>-0.03705065450328504</v>
-      </c>
-      <c r="DA15" t="n">
-        <v>-0.1469018032601682</v>
-      </c>
-      <c r="DB15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DE15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DF15" t="n">
-        <v>0.0861031547458173</v>
-      </c>
-      <c r="DG15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>-0.183248447160072</v>
-      </c>
-      <c r="DJ15" t="n">
-        <v>0.02432949244671894</v>
-      </c>
-      <c r="DK15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>0.05812385447650686</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>0.1247071200815989</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>0.0997609045992837</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX15" t="n">
-        <v>0.06781705311584026</v>
-      </c>
-      <c r="DY15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DZ15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EA15" t="n">
-        <v>-0.0300163601448277</v>
-      </c>
-      <c r="EB15" t="n">
-        <v>-0.05643828043096304</v>
-      </c>
-      <c r="EC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EE15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EF15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EG15" t="n">
-        <v>0.07613285877764718</v>
-      </c>
-      <c r="EH15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EJ15" t="n">
-        <v>-0.06592153539097424</v>
-      </c>
-      <c r="EK15" t="n">
-        <v>-0.1034955973012468</v>
-      </c>
-      <c r="EL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EP15" t="n">
-        <v>0.05849982068935675</v>
-      </c>
-      <c r="EQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="ER15" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES15" t="n">
-        <v>0.02821287917745455</v>
-      </c>
-      <c r="ET15" t="n">
-        <v>-0.0003578574784063377</v>
-      </c>
-      <c r="EU15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EV15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EX15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EY15" t="n">
-        <v>0.06193106658417517</v>
-      </c>
-      <c r="EZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB15" t="n">
-        <v>-0.03904311055780563</v>
-      </c>
-      <c r="FC15" t="n">
-        <v>-0.1337970341641347</v>
-      </c>
-      <c r="FD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FF15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FG15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FH15" t="n">
-        <v>0.04808725523091254</v>
-      </c>
-      <c r="FI15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="FK15" t="n">
-        <v>0.02495150915208932</v>
-      </c>
-      <c r="FL15" t="n">
-        <v>-0.1015816578314805</v>
-      </c>
-      <c r="FM15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FN15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FO15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FP15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FQ15" t="n">
-        <v>0.04366701635913742</v>
-      </c>
-      <c r="FR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="FS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="FT15" t="n">
-        <v>-0.0422578771060257</v>
-      </c>
-      <c r="FU15" t="n">
-        <v>-0.1753812882517644</v>
-      </c>
-      <c r="FV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="FW15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="FY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="FZ15" t="n">
-        <v>-0.04387011112429012</v>
-      </c>
-      <c r="GA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="GB15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="GC15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="GD15" t="n">
-        <v>0.1044987460110746</v>
-      </c>
-      <c r="GE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="GG15" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>0</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="CS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EJ16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EK16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="ER16" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="ET16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FC16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FK16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FT16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FU16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="FV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GG16" t="n">
         <v>0</v>
       </c>
     </row>
